--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G59"/>
+  <dimension ref="A1:G51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,60 +468,60 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Scientist III, Data Engineer</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thermo Fisher Scientific</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>26.4</v>
+        <v>18.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Redshift, Athena, S3, API Gateway, IAM, RDS</t>
+          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=242e2f2f15e944fd</t>
+          <t>https://www.indeed.com/viewjob?jk=1e68aed4fb5428da</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Platform Engineer (AWS)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e68aed4fb5428da</t>
+          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Cloud Software Engineer (Full-Stack)</t>
+          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,50 +548,50 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Anchorage, AK, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=716162d09810edc0</t>
+          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Platform Engineer (AWS)</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.3</v>
+        <v>13.9</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, DynamoDB, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, DataOps</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fff87f9ad2a13f8a</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5b89f5da184cb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Data Architect - C2H</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>TEEMA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Flower Mound, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, DataOps</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,7 +636,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5b89f5da184cb</t>
+          <t>https://www.indeed.com/viewjob?jk=a07fa9ddece4b00d</t>
         </is>
       </c>
     </row>
@@ -713,60 +713,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Software Engineer I (Full Stack) Java</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c75ad372a9b5c75</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Analytics Engineer II</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ConstructConnect</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,67 +776,67 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d47e5529ec2a3740</t>
+          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fb07338bf043f5b4</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer I (Full Stack) Java</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,59 +846,59 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Guidewire ETL Developer</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Informatica PowerCenter, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=add49e38a96075b6</t>
+          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Development Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,7 +951,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
         </is>
       </c>
     </row>
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56ec4b91bd2eae45</t>
+          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a2264d35d4610406</t>
+          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=05d5a587a6d14b89</t>
+          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=654e0c27326adde9</t>
+          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47c94da43a5f1ab3</t>
+          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ecf0f8c6cfd89ac</t>
+          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=115c597b804055b6</t>
+          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6ce3e7bea45493e</t>
+          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6fcd195523297efe</t>
+          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=86d26fa4197df309</t>
+          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efbb963d7b486eb3</t>
+          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be091eaed93c89d7</t>
+          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fded2db8fc850d7c</t>
+          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=864c1bb4125e2010</t>
+          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=04c7d7476e8c4a3d</t>
+          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6c9866f9bd84cc3</t>
+          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20ef5d7fa994bc4b</t>
+          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=077d100f577640d4</t>
+          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dcb817fc87f8be2</t>
+          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=508eae3571acb269</t>
+          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3408da3a2f2fb524</t>
+          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2fdbf484ba6d2466</t>
+          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c829b97ed54e6b32</t>
+          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=361032e756703c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a6ae978cfc3e463</t>
+          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4f4e1c6c825cd8a6</t>
+          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ae19fe28acac370</t>
+          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,102 +1931,102 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a56034ff2d0124a5</t>
+          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b60a01ac0f19294</t>
+          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2025-12-31</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7c3fbe0b81bbf8a</t>
+          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Sr. Professional, Software Engineering</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cotality</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=09197d183364a677</t>
+          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Development Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, IAM, RDS, Azure, Google Cloud Platform, GCP, Kafka, Splunk, CI/CD</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,137 +2071,137 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c3e80d85a4dac8</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Fullstack Engineer (Retool)</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Parser Limited</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Databricks, Unity Catalog, GCP, Spark, Scala, Data Modeling, Git</t>
+          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b8cf4f9a1850308</t>
+          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
+          <t>Dev Ops. Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-10</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
+          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AWS Public Cloud Engineer - Must have both AWS/Azure</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Google Cloud Platform, GCP, Oracle, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2025-12-31</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=756649818d5f3c4c</t>
+          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr. Professional, Software Engineering</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cotality</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Irvine, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, Scala, Kafka, Snowflake, Data Modeling, Tableau, CI/CD, Terraform</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Amazon QuickSight</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2210,286 +2210,6 @@
         </is>
       </c>
       <c r="G51" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7c2508b047fe2781</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Business Intelligence Analyst</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Leo Facilities Maintenance</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>West Chester, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D52" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Medallion Architecture, Scala, Snowflake, Data Modeling, Star Schema, ETL, Power BI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8e8d9e56b424a71d</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D53" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D54" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=268128188c94e0e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Azure Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Richmond, VA, US USA</t>
-        </is>
-      </c>
-      <c r="D55" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Kubernetes, AKS, Git</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a623f40b4389b47f</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D56" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=557e52ab1c5d0ec6</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Dev Ops. Architect</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D57" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Jenkins, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=86743c7261c69b6c</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Wecom Fiber</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D58" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D59" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Amazon QuickSight</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=d3b1cef4b777b5a5</t>
         </is>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,15 +548,15 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, DataOps</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5b89f5da184cb</t>
+          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Architect - C2H</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>TEEMA</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Flower Mound, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a07fa9ddece4b00d</t>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Software Engineer I (Full Stack) Java</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,102 +671,102 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer I (Full Stack) Java</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Analytics Engineer II</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ConstructConnect</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-10</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a17b4dda4590caa</t>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Wecom Fiber</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,182 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Lebanon, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Network Operations Trainee</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Snowflake, Oracle, ETL</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f9b6252d4232bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Wecom Fiber</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Amazon QuickSight</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b1cef4b777b5a5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,12 +503,12 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -517,11 +517,11 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>17.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,102 +531,102 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
+          <t>https://www.indeed.com/viewjob?jk=510e2092d20062f6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Power BI Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Legence</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.2</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c671fac5bf99b42</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Software Engineer I (Full Stack) Java</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
+          <t>Software Engineer I (Full Stack) Java</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Oracle</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,40 +741,110 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>New York Life</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Lebanon, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Oracle</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
           <t>Senior BI Developer &amp; Analytics Engineer</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>Wecom Fiber</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
-      <c r="D10" t="n">
+      <c r="D12" t="n">
         <v>10.4</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,7 +578,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ChowaCo</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -812,41 +812,6 @@
       <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior BI Developer &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Wecom Fiber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>RDS, Scala, Snowflake, clustering keys, ETL, Tableau, Tableau Server, AKS, Git, Python</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eea7ffbb16ef4f94</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G11"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, Tableau</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510e2092d20062f6</t>
+          <t>https://www.indeed.com/viewjob?jk=a49a54c48156d9f6</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Power BI Data Engineer</t>
+          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Legence</t>
+          <t>ChowaCo</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>17.4</v>
+        <v>14.6</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Dataflow, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c671fac5bf99b42</t>
+          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ChowaCo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
+          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
         </is>
       </c>
     </row>
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Software Engineer I (Full Stack) Java</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Walgreens</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Deerfield, IL, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Software Engineer I (Full Stack) Java</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,110 +706,75 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
+          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>Oracle</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Lebanon, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
+          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,105 +678,35 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, GCP, BigQuery, Scala, Snowflake, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f1a89b21bbe373b9</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Lebanon, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior Software Developer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Oracle</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Spark, Scala, Oracle, Splunk, CI/CD, Git, Python</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=77bccdac7a052a5f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Cloud Architect, ML/AI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Minnesota</t>
+          <t>DoiT</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, Tableau</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49a54c48156d9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7df305cb5baa7b</t>
         </is>
       </c>
     </row>
@@ -573,25 +573,25 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Eagan, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, Tableau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
+          <t>https://www.indeed.com/viewjob?jk=a49a54c48156d9f6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Okta</t>
+          <t>AWS Network Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -622,11 +622,11 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, DataOps</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+          <t>https://www.indeed.com/viewjob?jk=81b5b89f5da184cb</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer I (Full Stack) Java</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Walgreens</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Deerfield, IL, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,42 +671,217 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Okta</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Architect - C2H</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Flower Mound, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a07fa9ddece4b00d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Software Engineer I (Full Stack) Java</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Walgreens</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Deerfield, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>New York Life</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
-      <c r="D8" t="n">
+      <c r="D11" t="n">
         <v>11.1</v>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>2026-04-02</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Network Operations Trainee</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Snowflake, Oracle, ETL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4f9b6252d4232bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Amazon QuickSight</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3b1cef4b777b5a5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,25 +503,25 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Cloud Architect, ML/AI</t>
+          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>DoiT</t>
+          <t>ChowaCo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7df305cb5baa7b</t>
+          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ChowaCo</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2026-04-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
+          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Blue Cross and Blue Shield of Minnesota</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Eagan, MN, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>14.6</v>
+        <v>13.2</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, Tableau</t>
+          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,287 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a49a54c48156d9f6</t>
+          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Senior Associate, AWS Cloud Platform Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Lebanon, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, DataOps</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5b89f5da184cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Architect - C2H</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TEEMA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Flower Mound, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a07fa9ddece4b00d</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Software Engineer I (Full Stack) Java</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Walgreens</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Deerfield, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Oracle, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7e3e188fd3c8b1b5</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Lebanon, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Network Operations Trainee</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Snowflake, Oracle, ETL</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f9b6252d4232bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Amazon QuickSight</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b1cef4b777b5a5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,111 +532,6 @@
       <c r="G3" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8389dc038a61799a</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Okta</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, ECS, Databricks, Unity Catalog, Spark, Scala, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=229a363c5f9abe92</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Senior Associate, AWS Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>New York Life</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Lebanon, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, IAM, Databricks, Spark, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-02</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5130b1cac45762a</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,35 +503,105 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>Cloud/Drupal Subject Matter Specialist</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BFG Enterprise Services</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Suitland, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=890c6ef795b6dd39</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
           <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>ChowaCo</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>US USA</t>
         </is>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>14.6</v>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>SAP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cloud/Drupal Subject Matter Specialist</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BFG Enterprise Services</t>
+          <t>Villanova University</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Suitland, MD, US USA</t>
+          <t>Villanova, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-04-12</t>
+          <t>2025-03-23</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=890c6ef795b6dd39</t>
+          <t>https://www.indeed.com/viewjob?jk=5cdea475a3468daf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
+          <t>Senior Cloud Architect, ML/AI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ChowaCo</t>
+          <t>DoiT</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Azure</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,287 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7df305cb5baa7b</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>Cloud/Drupal Subject Matter Specialist</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>BFG Enterprise Services</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Suitland, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=890c6ef795b6dd39</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ChowaCo</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Blue Cross and Blue Shield of Minnesota</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Eagan, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>14.6</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, Tableau</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a49a54c48156d9f6</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, DataOps</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81b5b89f5da184cb</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Data Architect - C2H</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>TEEMA</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Flower Mound, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a07fa9ddece4b00d</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B10" t="inlineStr">
         <is>
           <t>SAP</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Austin, TX, US USA</t>
         </is>
       </c>
-      <c r="D5" t="n">
+      <c r="D10" t="n">
         <v>11.8</v>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E10" t="inlineStr">
         <is>
           <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>2026-04-12</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Network Operations Trainee</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Snowflake, Oracle, ETL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c4f9b6252d4232bb</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>GA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Amazon QuickSight</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d3b1cef4b777b5a5</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-04-12.xlsx
+++ b/results/job_matches_2026-04-12.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,385 +468,70 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AWS Network Engineer</t>
+          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>ChowaCo</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Lambda, Kinesis, Redshift, Athena, S3, RDS, Hadoop</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e68aed4fb5428da</t>
+          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Villanova University</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Villanova, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>16.7</v>
+        <v>11.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, Scala, Kafka, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2025-03-23</t>
+          <t>2026-04-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5cdea475a3468daf</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Senior Cloud Architect, ML/AI</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>DoiT</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Redshift, Step Functions, S3, API Gateway, IAM, RDS, Azure</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7df305cb5baa7b</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cloud/Drupal Subject Matter Specialist</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>BFG Enterprise Services</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Suitland, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
-        <v>15.3</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Oracle, PostgreSQL, MySQL, MongoDB, NoSQL</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=890c6ef795b6dd39</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Full Stack Developer - Contract Hire (Remote, US Only)</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>ChowaCo</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Unity Catalog, GCP, BigQuery, PostgreSQL</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=080c153a60c2db6d</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Senior AI Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Blue Cross and Blue Shield of Minnesota</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Eagan, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>14.6</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Azure, GCP, Scala, Tableau</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a49a54c48156d9f6</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.9</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, DynamoDB, NoSQL, DataOps</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81b5b89f5da184cb</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Data Architect - C2H</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>TEEMA</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Flower Mound, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Scala, Snowflake, Databricks Lakehouse, Dimensional Modeling</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a07fa9ddece4b00d</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>SAP</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AWS, S3, IAM, RDS, Azure, GCP, Cloud Storage, Scala, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-04-12</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=c08fc820fe10f7ed</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Network Operations Trainee</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, IAM, RDS, Snowflake, Oracle, ETL</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c4f9b6252d4232bb</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>GA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Redshift, Athena, S3, RDS, Scala, Data Modeling, ETL, Amazon QuickSight</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-04-11</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d3b1cef4b777b5a5</t>
         </is>
       </c>
     </row>
